--- a/survey_templates/041_office_cleanliness_feedback_form--survey_templates.xlsx
+++ b/survey_templates/041_office_cleanliness_feedback_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'break_room'}</t>
+          <t>break_room</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Break Room'}</t>
+          <t>Break Room</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'kitchen'}</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Kitchen'}</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'meeting_room'}</t>
+          <t>meeting_room</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Meeting Room'}</t>
+          <t>Meeting Room</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_very_dirty'}</t>
+          <t>1_-_very_dirty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1 - Very Dirty'}</t>
+          <t>1 - Very Dirty</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_dirty'}</t>
+          <t>2_-_somewhat_dirty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat Dirty'}</t>
+          <t>2 - Somewhat Dirty</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_clean'}</t>
+          <t>4_-_somewhat_clean</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat Clean'}</t>
+          <t>4 - Somewhat Clean</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_extremely_clean'}</t>
+          <t>5_-_extremely_clean</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '5 - Extremely Clean'}</t>
+          <t>5 - Extremely Clean</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'trash_and_recycling'}</t>
+          <t>trash_and_recycling</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Trash and Recycling'}</t>
+          <t>Trash and Recycling</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'disinfecting_and_sanitizing'}</t>
+          <t>disinfecting_and_sanitizing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Disinfecting and Sanitizing'}</t>
+          <t>Disinfecting and Sanitizing</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'cleaning_equipment_and_supplies'}</t>
+          <t>cleaning_equipment_and_supplies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Cleaning Equipment and Supplies'}</t>
+          <t>Cleaning Equipment and Supplies</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
